--- a/Evaluación-fase-1/Matriz de poder.xlsx
+++ b/Evaluación-fase-1/Matriz de poder.xlsx
@@ -83,7 +83,7 @@
     <t>Directa</t>
   </si>
   <si>
-    <t>Contar con información consolidada de las compañías, inventarios, unidades, check in, mantenimientos y reportes.</t>
+    <t>Informacion consolidada de inventarios, unidades, check in, mantenimiento y reportes, distinguir stock propio de Comandancia y entregas a companias con salida y recepcion trazables.</t>
   </si>
   <si>
     <t>Gestionar de cerca</t>
@@ -104,13 +104,13 @@
     <t>STK-02</t>
   </si>
   <si>
-    <t>Superintendencia / administración institucional</t>
+    <t>Superintendencia / administración de Bomberos</t>
   </si>
   <si>
     <t>Stakeholders de apoyo y gestión</t>
   </si>
   <si>
-    <t>Gestión institucional, control de recursos y decisiones generales</t>
+    <t>Gestión de Bomberos, control de recursos y decisiones generales</t>
   </si>
   <si>
     <t>Medio</t>
@@ -119,7 +119,7 @@
     <t>Indirecta</t>
   </si>
   <si>
-    <t>Tener visibilidad del uso y estado de los recursos y contar con información útil para decisiones institucionales.</t>
+    <t>Tener visibilidad del uso y estado de los recursos y contar con información útil para decisiones de Bomberos.</t>
   </si>
   <si>
     <t>Mantener satisfecho</t>
@@ -134,7 +134,7 @@
     <t>Equipo Capstone / Comandancia</t>
   </si>
   <si>
-    <t>Estructura institucional del CBSB</t>
+    <t>Estructura de Bomberos de San Bernardo</t>
   </si>
   <si>
     <t>STK-03</t>
@@ -146,7 +146,7 @@
     <t>Unidades organizacionales que administran sus propios recursos</t>
   </si>
   <si>
-    <t>Gestionar inventario, unidades y movimientos propios sin mezclar información con otras compañías.</t>
+    <t>Gestionar inventario, unidades y movimientos propios, el maquinista registra el check in diario y el capitan supervisa cumplimiento y historial de su compania. Permisos concretos por validar.</t>
   </si>
   <si>
     <t>Revisión de avances + demostraciones</t>
@@ -167,7 +167,7 @@
     <t>Operación y control del inventario y equipamiento</t>
   </si>
   <si>
-    <t>Registrar y consultar artículos, cantidades, series, estados, ubicaciones, altas, bajas y pérdidas con trazabilidad.</t>
+    <t>Registrar articulos, cantidades, series, estados, ubicaciones, bajas y perdidas, contemplar al inspector de Material Menor y entregas de Comandancia con recepcion vinculada, segun permisos por validar.</t>
   </si>
   <si>
     <t>Mantener informado</t>
@@ -191,7 +191,7 @@
     <t>Gestión de carros, unidades, revisiones y mantenimientos</t>
   </si>
   <si>
-    <t>Controlar unidades, kilometraje, horas, check in, historial técnico, mantenimiento preventivo/correctivo y alertas.</t>
+    <t>Controlar unidades, kilometraje, horas y alertas, el inspector documenta mantenimiento, pruebas y fotos anteriores y posteriores. Distinguir conformidad del capitan de cierre tecnico, pendiente de definir.</t>
   </si>
   <si>
     <t>Validación funcional + revisión de avances</t>
@@ -206,7 +206,7 @@
     <t>Bomberos / voluntarios</t>
   </si>
   <si>
-    <t>Personas asociadas al equipamiento entregado y a la operación institucional</t>
+    <t>Personas asociadas al equipamiento entregado y a la operación de Bomberos</t>
   </si>
   <si>
     <t>Bajo</t>
@@ -239,7 +239,7 @@
     <t>Directa técnica</t>
   </si>
   <si>
-    <t>Disponer de una solución instalable en servidor local, con acceso por red interna, respaldo y posibilidad de recuperación.</t>
+    <t>Validar servidor, red interna y acceso remoto seguro desde computadores, telefonos y tablets, capacidad para fotos historicas, respaldo y recuperacion. Infraestructura, sesiones y responsables por confirmar.</t>
   </si>
   <si>
     <t>Coordinación técnica + documentación</t>
@@ -329,7 +329,7 @@
     <t>STK-11</t>
   </si>
   <si>
-    <t>Bomberos de Chile / organismos de control</t>
+    <t>Bomberos de San Bernardo / organismos de control</t>
   </si>
   <si>
     <t>Contexto institucional, control patrimonial y eventual fiscalización</t>
@@ -437,7 +437,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -462,8 +462,17 @@
     <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -472,6 +481,9 @@
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2663,7 +2675,7 @@
       <c r="I5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="8" t="s">
         <v>23</v>
       </c>
       <c r="K5" s="5" t="s">
@@ -2683,49 +2695,49 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="12" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2757,7 +2769,7 @@
       <c r="I7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="8" t="s">
         <v>44</v>
       </c>
       <c r="K7" s="5" t="s">
@@ -2777,49 +2789,49 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="L8" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="M8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="N8" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="13" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2851,7 +2863,7 @@
       <c r="I9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="8" t="s">
         <v>59</v>
       </c>
       <c r="K9" s="5" t="s">
@@ -2871,49 +2883,49 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="L10" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="M10" s="8" t="s">
+      <c r="M10" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="N10" s="8" t="s">
+      <c r="N10" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="O10" s="10" t="s">
+      <c r="O10" s="13" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2945,7 +2957,7 @@
       <c r="I11" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="8" t="s">
         <v>75</v>
       </c>
       <c r="K11" s="5" t="s">
@@ -2965,49 +2977,49 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="L12" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="N12" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="O12" s="10" t="s">
+      <c r="O12" s="13" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3059,49 +3071,49 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="J14" s="10" t="s">
+      <c r="J14" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="K14" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="L14" s="10" t="s">
+      <c r="L14" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="M14" s="8" t="s">
+      <c r="M14" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="N14" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="O14" s="10" t="s">
+      <c r="O14" s="13" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3109,7 +3121,7 @@
       <c r="A15" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="15" t="s">
         <v>105</v>
       </c>
       <c r="C15" s="5" t="s">
